--- a/storage/app/templates/extrato_template.xlsx
+++ b/storage/app/templates/extrato_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="14460"/>
+    <workbookView windowHeight="15880"/>
   </bookViews>
   <sheets>
     <sheet name="extrato_matt_20260508_233355" sheetId="1" r:id="rId1"/>
@@ -29,74 +29,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF800080"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Saldo {NOME} R$ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF800080"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>X.XXX</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF800080"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>,XX</t>
-    </r>
+    <t>Saldo {NOME} R$ X.XXX,XX</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">U$ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>X.XXX</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>,00</t>
-    </r>
+    <t>U$ X.XXX,00</t>
   </si>
   <si>
     <t>Entrada R$</t>
@@ -145,7 +81,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -163,38 +99,38 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -346,24 +282,6 @@
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF1155CC"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="35">
@@ -1023,41 +941,59 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1534,29 +1470,29 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultColWidth="12.6339285714286" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="11" max="11" width="29.1607142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="F1" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="19" t="s">
+      <c r="I1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="22"/>
     </row>
     <row r="2" customHeight="1" spans="1:12">
       <c r="A2" s="3" t="s">
@@ -1571,12 +1507,12 @@
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="12"/>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="23" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="4"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="20"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="22"/>
     </row>
     <row r="3" customHeight="1" spans="1:12">
       <c r="A3" s="5" t="s">
@@ -1609,10 +1545,10 @@
       <c r="J3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="20"/>
+      <c r="L3" s="22"/>
     </row>
     <row r="4" customHeight="1" spans="1:12">
       <c r="A4" s="7">
@@ -1627,8 +1563,8 @@
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
       <c r="J4" s="8"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="20"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="22"/>
     </row>
     <row r="5" customHeight="1" spans="1:12">
       <c r="A5" s="7">
@@ -1643,8 +1579,8 @@
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="20"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="22"/>
     </row>
     <row r="6" customHeight="1" spans="1:12">
       <c r="A6" s="7">
@@ -1659,8 +1595,8 @@
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
       <c r="J6" s="8"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="20"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" customHeight="1" spans="1:12">
       <c r="A7" s="7">
@@ -1675,8 +1611,8 @@
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="20"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="22"/>
     </row>
     <row r="8" customHeight="1" spans="1:12">
       <c r="A8" s="7">
@@ -1691,8 +1627,8 @@
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
       <c r="J8" s="8"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="20"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="22"/>
     </row>
     <row r="9" customHeight="1" spans="1:12">
       <c r="A9" s="7">
@@ -1707,8 +1643,8 @@
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
       <c r="J9" s="8"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="20"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="22"/>
     </row>
     <row r="10" customHeight="1" spans="1:12">
       <c r="A10" s="7" t="s">
@@ -1723,8 +1659,8 @@
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
       <c r="J10" s="8"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="20"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="22"/>
     </row>
     <row r="11" customHeight="1" spans="1:12">
       <c r="A11" s="9"/>
@@ -1745,23 +1681,24 @@
       <c r="J11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="25"/>
-      <c r="L11" s="20"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="22"/>
     </row>
     <row r="19" customHeight="1" spans="10:10">
-      <c r="J19" s="26"/>
+      <c r="J19" s="28"/>
+    </row>
+    <row r="21" customHeight="1" spans="7:7">
+      <c r="G21" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:J1"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" display="Saldo {NOME} R$ X.XXX,XX"/>
-    <hyperlink ref="K1" r:id="rId1" display="U$ X.XXX,00"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
